--- a/public/static/客户产品价格导入模板.xlsx
+++ b/public/static/客户产品价格导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="31245" windowHeight="12030"/>
   </bookViews>
   <sheets>
     <sheet name="客户产品价格" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>序号</t>
   </si>
@@ -48,7 +48,7 @@
     <t>税率(%)</t>
   </si>
   <si>
-    <t>有效日期起</t>
+    <t>有效日期起(必填)</t>
   </si>
   <si>
     <t>有效日期止(必填)</t>
@@ -82,9 +82,6 @@
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>100</t>
   </si>
   <si>
     <t xml:space="preserve">说明：
@@ -1322,17 +1319,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="9.22222222222222" customWidth="1"/>
-    <col min="2" max="2" width="17.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="9.225" customWidth="1"/>
+    <col min="2" max="2" width="17.1083333333333" customWidth="1"/>
     <col min="3" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="20" style="2" customWidth="1"/>
-    <col min="6" max="7" width="13.2222222222222" customWidth="1"/>
-    <col min="8" max="8" width="18.8888888888889" customWidth="1"/>
-    <col min="9" max="13" width="13.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="13.225" customWidth="1"/>
+    <col min="7" max="7" width="20.125" customWidth="1"/>
+    <col min="8" max="8" width="18.8916666666667" customWidth="1"/>
+    <col min="9" max="13" width="13.225" customWidth="1"/>
     <col min="14" max="16" width="14.3333333333333" customWidth="1"/>
-    <col min="17" max="17" width="29.1111111111111" customWidth="1"/>
+    <col min="17" max="17" width="29.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:17">
@@ -1395,9 +1393,7 @@
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="E2" s="6"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -1421,14 +1417,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="131.777777777778" customWidth="1"/>
+    <col min="1" max="1" width="131.775" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="96" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1"/>

--- a/public/static/客户产品价格导入模板.xlsx
+++ b/public/static/客户产品价格导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31245" windowHeight="12030"/>
+    <workbookView windowWidth="31485" windowHeight="12615"/>
   </bookViews>
   <sheets>
     <sheet name="客户产品价格" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>序号</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>单价(含税)</t>
+  </si>
+  <si>
+    <t>单价(不含税)</t>
   </si>
   <si>
     <t>税率(%)</t>
@@ -1318,22 +1321,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="2" width="17.1083333333333" customWidth="1"/>
     <col min="3" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="20" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.225" customWidth="1"/>
-    <col min="7" max="7" width="20.125" customWidth="1"/>
-    <col min="8" max="8" width="18.8916666666667" customWidth="1"/>
-    <col min="9" max="13" width="13.225" customWidth="1"/>
-    <col min="14" max="16" width="14.3333333333333" customWidth="1"/>
-    <col min="17" max="17" width="29.1083333333333" customWidth="1"/>
+    <col min="6" max="6" width="29.375" customWidth="1"/>
+    <col min="7" max="7" width="13.225" customWidth="1"/>
+    <col min="8" max="8" width="20.125" customWidth="1"/>
+    <col min="9" max="9" width="18.8916666666667" customWidth="1"/>
+    <col min="10" max="14" width="13.225" customWidth="1"/>
+    <col min="15" max="17" width="14.3333333333333" customWidth="1"/>
+    <col min="18" max="18" width="29.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:17">
+    <row r="1" ht="25" customHeight="1" spans="1:18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1349,7 +1353,7 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -1385,10 +1389,13 @@
       <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:17">
+    <row r="2" ht="20" customHeight="1" spans="1:18">
       <c r="A2" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -1406,6 +1413,7 @@
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1424,7 +1432,7 @@
   <sheetData>
     <row r="1" ht="96" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1"/>

--- a/public/static/客户产品价格导入模板.xlsx
+++ b/public/static/客户产品价格导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31485" windowHeight="12615"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="客户产品价格" sheetId="1" r:id="rId1"/>
@@ -28,18 +28,75 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>序号</t>
   </si>
   <si>
-    <t>客户编码(必填)</t>
-  </si>
-  <si>
-    <t>客户料号(必填)</t>
-  </si>
-  <si>
-    <t>品名规格(必填)</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客户编码</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(必填)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客户料号</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(必填)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>品名规格</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(必填)</t>
+    </r>
   </si>
   <si>
     <t>单价(含税)</t>
@@ -51,10 +108,48 @@
     <t>税率(%)</t>
   </si>
   <si>
-    <t>有效日期起(必填)</t>
-  </si>
-  <si>
-    <t>有效日期止(必填)</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有效日期起</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(必填)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有效日期止</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(必填)</t>
+    </r>
   </si>
   <si>
     <t>打字内容</t>
@@ -79,6 +174,18 @@
   </si>
   <si>
     <t>特殊要求</t>
+  </si>
+  <si>
+    <t>保持架材质</t>
+  </si>
+  <si>
+    <t>密封盖颜色</t>
+  </si>
+  <si>
+    <t>凸出量</t>
+  </si>
+  <si>
+    <t>预负荷</t>
   </si>
   <si>
     <t>备注</t>
@@ -103,7 +210,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -126,6 +233,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
@@ -287,6 +401,13 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -621,152 +742,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -779,13 +900,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1321,48 +1445,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="9.225" customWidth="1"/>
-    <col min="2" max="2" width="17.1083333333333" customWidth="1"/>
+    <col min="1" max="1" width="9.22222222222222" customWidth="1"/>
+    <col min="2" max="2" width="17.1111111111111" customWidth="1"/>
     <col min="3" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="20" style="2" customWidth="1"/>
-    <col min="6" max="6" width="29.375" customWidth="1"/>
-    <col min="7" max="7" width="13.225" customWidth="1"/>
-    <col min="8" max="8" width="20.125" customWidth="1"/>
-    <col min="9" max="9" width="18.8916666666667" customWidth="1"/>
-    <col min="10" max="14" width="13.225" customWidth="1"/>
-    <col min="15" max="17" width="14.3333333333333" customWidth="1"/>
-    <col min="18" max="18" width="29.1083333333333" customWidth="1"/>
+    <col min="6" max="6" width="29.3796296296296" customWidth="1"/>
+    <col min="7" max="7" width="13.2222222222222" customWidth="1"/>
+    <col min="8" max="8" width="20.1296296296296" customWidth="1"/>
+    <col min="9" max="9" width="18.8888888888889" customWidth="1"/>
+    <col min="10" max="14" width="13.2222222222222" customWidth="1"/>
+    <col min="15" max="20" width="14.3333333333333" customWidth="1"/>
+    <col min="21" max="21" width="15.4444444444444" customWidth="1"/>
+    <col min="22" max="22" width="29.1111111111111" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:18">
+    <row r="1" ht="25" customHeight="1" spans="1:22">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
@@ -1392,28 +1517,44 @@
       <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:18">
-      <c r="A2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
+    <row r="2" ht="20" customHeight="1" spans="1:22">
+      <c r="A2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1425,14 +1566,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="131.775" customWidth="1"/>
+    <col min="1" max="1" width="131.777777777778" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="96" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1"/>

--- a/public/static/客户产品价格导入模板.xlsx
+++ b/public/static/客户产品价格导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="客户产品价格" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>序号</t>
   </si>
@@ -186,6 +186,12 @@
   </si>
   <si>
     <t>预负荷</t>
+  </si>
+  <si>
+    <t>角度</t>
+  </si>
+  <si>
+    <t>钢球/中心径/倒角</t>
   </si>
   <si>
     <t>备注</t>
@@ -1445,24 +1451,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="9.22222222222222" customWidth="1"/>
-    <col min="2" max="2" width="17.1111111111111" customWidth="1"/>
+    <col min="1" max="1" width="9.225" customWidth="1"/>
+    <col min="2" max="2" width="17.1083333333333" customWidth="1"/>
     <col min="3" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="20" style="2" customWidth="1"/>
-    <col min="6" max="6" width="29.3796296296296" customWidth="1"/>
-    <col min="7" max="7" width="13.2222222222222" customWidth="1"/>
-    <col min="8" max="8" width="20.1296296296296" customWidth="1"/>
-    <col min="9" max="9" width="18.8888888888889" customWidth="1"/>
-    <col min="10" max="14" width="13.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="29.3833333333333" customWidth="1"/>
+    <col min="7" max="7" width="13.225" customWidth="1"/>
+    <col min="8" max="8" width="20.1333333333333" customWidth="1"/>
+    <col min="9" max="9" width="18.8916666666667" customWidth="1"/>
+    <col min="10" max="14" width="13.225" customWidth="1"/>
     <col min="15" max="20" width="14.3333333333333" customWidth="1"/>
-    <col min="21" max="21" width="15.4444444444444" customWidth="1"/>
-    <col min="22" max="22" width="29.1111111111111" customWidth="1"/>
+    <col min="21" max="22" width="15.4416666666667" customWidth="1"/>
+    <col min="23" max="24" width="29.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:22">
+    <row r="1" ht="25" customHeight="1" spans="1:24">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1529,10 +1535,16 @@
       <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="W1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:22">
+    <row r="2" ht="20" customHeight="1" spans="1:24">
       <c r="A2" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -1555,6 +1567,8 @@
       <c r="T2" s="6"/>
       <c r="U2" s="6"/>
       <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1566,14 +1580,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="131.777777777778" customWidth="1"/>
+    <col min="1" max="1" width="131.775" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="96" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1"/>

--- a/public/static/客户产品价格导入模板.xlsx
+++ b/public/static/客户产品价格导入模板.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>序号</t>
   </si>
@@ -97,6 +97,9 @@
       </rPr>
       <t>(必填)</t>
     </r>
+  </si>
+  <si>
+    <t>配对方式</t>
   </si>
   <si>
     <t>单价(含税)</t>
@@ -1451,24 +1454,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="2" width="17.1083333333333" customWidth="1"/>
     <col min="3" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="20" style="2" customWidth="1"/>
-    <col min="6" max="6" width="29.3833333333333" customWidth="1"/>
-    <col min="7" max="7" width="13.225" customWidth="1"/>
-    <col min="8" max="8" width="20.1333333333333" customWidth="1"/>
-    <col min="9" max="9" width="18.8916666666667" customWidth="1"/>
-    <col min="10" max="14" width="13.225" customWidth="1"/>
-    <col min="15" max="20" width="14.3333333333333" customWidth="1"/>
-    <col min="21" max="22" width="15.4416666666667" customWidth="1"/>
-    <col min="23" max="24" width="29.1083333333333" customWidth="1"/>
+    <col min="5" max="6" width="20" style="2" customWidth="1"/>
+    <col min="7" max="7" width="29.3833333333333" customWidth="1"/>
+    <col min="8" max="8" width="13.225" customWidth="1"/>
+    <col min="9" max="9" width="20.1333333333333" customWidth="1"/>
+    <col min="10" max="10" width="18.8916666666667" customWidth="1"/>
+    <col min="11" max="15" width="13.225" customWidth="1"/>
+    <col min="16" max="21" width="14.3333333333333" customWidth="1"/>
+    <col min="22" max="23" width="15.4416666666667" customWidth="1"/>
+    <col min="24" max="25" width="29.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:24">
+    <row r="1" ht="25" customHeight="1" spans="1:25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1487,16 +1490,16 @@
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1541,16 +1544,19 @@
       <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:24">
+    <row r="2" ht="20" customHeight="1" spans="1:25">
       <c r="A2" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7"/>
-      <c r="F2" s="6"/>
+      <c r="F2" s="7"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
@@ -1569,6 +1575,7 @@
       <c r="V2" s="6"/>
       <c r="W2" s="6"/>
       <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1587,7 +1594,7 @@
   <sheetData>
     <row r="1" ht="96" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1"/>
